--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from 52-100" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
+++ b/docs/ValueSet-VSVFOutMedRequestStatus-vista.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
